--- a/target.xlsx
+++ b/target.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\백업폴더\딱따구리\AI\강북도매 영업관리 포털\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38651BEB-E238-4782-BA3D-DDB01270892A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33180A0-2C35-48DF-97CC-DBDDC0D5EFC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F51F585E-D8DA-4EE1-A615-D4BBA305B88C}"/>
   </bookViews>
@@ -1254,58 +1254,58 @@
         <v>1</v>
       </c>
       <c r="B2" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" s="6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2" s="6">
         <v>0</v>
       </c>
       <c r="H2" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M2" s="6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" s="6">
         <v>0</v>
       </c>
       <c r="O2" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P2" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q2" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S2" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T2" s="6">
         <v>27</v>
@@ -1314,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W2" s="6">
         <v>21</v>
@@ -1326,7 +1326,7 @@
         <v>20</v>
       </c>
       <c r="Z2" s="6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="6">
         <v>0</v>
@@ -1335,10 +1335,10 @@
         <v>0</v>
       </c>
       <c r="AC2" s="6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AD2" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE2" s="6">
         <v>21</v>
@@ -1349,16 +1349,16 @@
         <v>0</v>
       </c>
       <c r="B3" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="6">
         <v>24</v>
@@ -1367,19 +1367,19 @@
         <v>0</v>
       </c>
       <c r="H3" s="6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I3" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K3" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L3" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M3" s="6">
         <v>24</v>
@@ -1388,7 +1388,7 @@
         <v>0</v>
       </c>
       <c r="O3" s="6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P3" s="6">
         <v>19</v>
@@ -1412,16 +1412,16 @@
         <v>28</v>
       </c>
       <c r="W3" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X3" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y3" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z3" s="6">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="6">
         <v>0</v>
@@ -1430,13 +1430,13 @@
         <v>0</v>
       </c>
       <c r="AC3" s="6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AD3" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE3" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.45">
@@ -1462,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I4" s="6">
         <v>15</v>
@@ -1471,10 +1471,10 @@
         <v>15</v>
       </c>
       <c r="K4" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L4" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M4" s="6">
         <v>19</v>
@@ -1486,16 +1486,16 @@
         <v>22</v>
       </c>
       <c r="P4" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q4" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R4" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S4" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T4" s="6">
         <v>19</v>
@@ -1507,16 +1507,16 @@
         <v>22</v>
       </c>
       <c r="W4" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X4" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y4" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z4" s="6">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="6">
         <v>0</v>
@@ -1525,13 +1525,13 @@
         <v>0</v>
       </c>
       <c r="AC4" s="6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AD4" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE4" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.45">
@@ -1539,16 +1539,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" s="6">
         <v>27</v>
@@ -1557,13 +1557,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J5" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" s="6">
         <v>21</v>
@@ -1578,19 +1578,19 @@
         <v>0</v>
       </c>
       <c r="O5" s="6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P5" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q5" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R5" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S5" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T5" s="6">
         <v>27</v>
@@ -1599,19 +1599,19 @@
         <v>0</v>
       </c>
       <c r="V5" s="6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="W5" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X5" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y5" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z5" s="6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="6">
         <v>0</v>
@@ -1620,13 +1620,13 @@
         <v>0</v>
       </c>
       <c r="AC5" s="6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AD5" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE5" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.45">
@@ -1634,16 +1634,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="6">
         <v>23</v>
@@ -1652,19 +1652,19 @@
         <v>0</v>
       </c>
       <c r="H6" s="6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I6" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K6" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L6" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M6" s="6">
         <v>23</v>
@@ -1673,10 +1673,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P6" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q6" s="6">
         <v>17</v>
@@ -1688,13 +1688,13 @@
         <v>17</v>
       </c>
       <c r="T6" s="6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U6" s="6">
         <v>0</v>
       </c>
       <c r="V6" s="6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="W6" s="6">
         <v>17</v>
@@ -1706,7 +1706,7 @@
         <v>17</v>
       </c>
       <c r="Z6" s="6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="6">
         <v>0</v>
@@ -1715,13 +1715,13 @@
         <v>0</v>
       </c>
       <c r="AC6" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AD6" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE6" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.45">
@@ -1729,16 +1729,16 @@
         <v>8</v>
       </c>
       <c r="B7" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" s="6">
         <v>33</v>
@@ -1747,19 +1747,19 @@
         <v>0</v>
       </c>
       <c r="H7" s="6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I7" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J7" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K7" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L7" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M7" s="6">
         <v>33</v>
@@ -1768,19 +1768,19 @@
         <v>0</v>
       </c>
       <c r="O7" s="6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P7" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q7" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R7" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S7" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T7" s="6">
         <v>33</v>
@@ -1789,19 +1789,19 @@
         <v>0</v>
       </c>
       <c r="V7" s="6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="W7" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X7" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y7" s="6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z7" s="6">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="6">
         <v>0</v>
@@ -1810,13 +1810,13 @@
         <v>0</v>
       </c>
       <c r="AC7" s="6">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AD7" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE7" s="6">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.45">
@@ -1836,13 +1836,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" s="6">
         <v>0</v>
       </c>
       <c r="H8" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I8" s="6">
         <v>17</v>
@@ -1857,34 +1857,34 @@
         <v>17</v>
       </c>
       <c r="M8" s="6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N8" s="6">
         <v>0</v>
       </c>
       <c r="O8" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P8" s="6">
         <v>17</v>
       </c>
       <c r="Q8" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R8" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S8" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T8" s="6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U8" s="6">
         <v>0</v>
       </c>
       <c r="V8" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W8" s="6">
         <v>17</v>
@@ -1893,10 +1893,10 @@
         <v>17</v>
       </c>
       <c r="Y8" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z8" s="6">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="6">
         <v>0</v>
@@ -1905,13 +1905,13 @@
         <v>0</v>
       </c>
       <c r="AC8" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AD8" s="6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE8" s="6">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.45">
@@ -1931,13 +1931,13 @@
         <v>15</v>
       </c>
       <c r="F9" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G9" s="6">
         <v>0</v>
       </c>
       <c r="H9" s="6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I9" s="6">
         <v>15</v>
@@ -1952,13 +1952,13 @@
         <v>15</v>
       </c>
       <c r="M9" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N9" s="6">
         <v>0</v>
       </c>
       <c r="O9" s="6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P9" s="6">
         <v>15</v>
@@ -1973,13 +1973,13 @@
         <v>15</v>
       </c>
       <c r="T9" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U9" s="6">
         <v>0</v>
       </c>
       <c r="V9" s="6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="W9" s="6">
         <v>15</v>
@@ -1988,10 +1988,10 @@
         <v>15</v>
       </c>
       <c r="Y9" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z9" s="6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="6">
         <v>0</v>
@@ -2000,13 +2000,13 @@
         <v>0</v>
       </c>
       <c r="AC9" s="6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AD9" s="6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AE9" s="6">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.45">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="F10" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G10" s="6">
         <v>0</v>
       </c>
       <c r="H10" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I10" s="6">
         <v>16</v>
@@ -2047,13 +2047,13 @@
         <v>16</v>
       </c>
       <c r="M10" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N10" s="6">
         <v>0</v>
       </c>
       <c r="O10" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P10" s="6">
         <v>16</v>
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="T10" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U10" s="6">
         <v>0</v>
       </c>
       <c r="V10" s="6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="W10" s="6">
         <v>16</v>
@@ -2083,10 +2083,10 @@
         <v>16</v>
       </c>
       <c r="Y10" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z10" s="6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="6">
         <v>0</v>
@@ -2095,13 +2095,13 @@
         <v>0</v>
       </c>
       <c r="AC10" s="6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AD10" s="6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AE10" s="6">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2247,10 +2247,10 @@
         <v>6</v>
       </c>
       <c r="J2" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L2" s="3">
         <v>6</v>
@@ -2274,7 +2274,7 @@
         <v>6</v>
       </c>
       <c r="S2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T2" s="3">
         <v>7</v>
@@ -2286,16 +2286,16 @@
         <v>8</v>
       </c>
       <c r="W2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z2" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="3">
         <v>0</v>
@@ -2304,13 +2304,13 @@
         <v>0</v>
       </c>
       <c r="AC2" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.45">
@@ -2336,13 +2336,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I3" s="3">
         <v>6</v>
       </c>
       <c r="J3" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3" s="3">
         <v>6</v>
@@ -2357,7 +2357,7 @@
         <v>0</v>
       </c>
       <c r="O3" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P3" s="3">
         <v>6</v>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W3" s="3">
         <v>6</v>
@@ -2390,7 +2390,7 @@
         <v>6</v>
       </c>
       <c r="Z3" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="3">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="AC3" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD3" s="3">
         <v>6</v>
@@ -2434,13 +2434,13 @@
         <v>8</v>
       </c>
       <c r="I4" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K4" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L4" s="3">
         <v>5</v>
@@ -2485,7 +2485,7 @@
         <v>5</v>
       </c>
       <c r="Z4" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="3">
         <v>0</v>
@@ -2494,7 +2494,7 @@
         <v>0</v>
       </c>
       <c r="AC4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD4" s="3">
         <v>5</v>
@@ -2508,16 +2508,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="3">
         <v>7</v>
@@ -2526,7 +2526,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5" s="3">
         <v>5</v>
@@ -2538,7 +2538,7 @@
         <v>5</v>
       </c>
       <c r="L5" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5" s="3">
         <v>7</v>
@@ -2547,16 +2547,16 @@
         <v>0</v>
       </c>
       <c r="O5" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P5" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q5" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R5" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S5" s="3">
         <v>6</v>
@@ -2580,7 +2580,7 @@
         <v>6</v>
       </c>
       <c r="Z5" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="3">
         <v>0</v>
@@ -2627,10 +2627,10 @@
         <v>6</v>
       </c>
       <c r="J6" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K6" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L6" s="3">
         <v>6</v>
@@ -2654,7 +2654,7 @@
         <v>6</v>
       </c>
       <c r="S6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T6" s="3">
         <v>7</v>
@@ -2666,16 +2666,16 @@
         <v>8</v>
       </c>
       <c r="W6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z6" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="3">
         <v>0</v>
@@ -2684,13 +2684,13 @@
         <v>0</v>
       </c>
       <c r="AC6" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.45">
@@ -2728,7 +2728,7 @@
         <v>7</v>
       </c>
       <c r="L7" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M7" s="3">
         <v>10</v>
@@ -2740,16 +2740,16 @@
         <v>11</v>
       </c>
       <c r="P7" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q7" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R7" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S7" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T7" s="3">
         <v>10</v>
@@ -2770,7 +2770,7 @@
         <v>7</v>
       </c>
       <c r="Z7" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="3">
         <v>0</v>
@@ -2782,10 +2782,10 @@
         <v>11</v>
       </c>
       <c r="AD7" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE7" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.45">
@@ -2811,28 +2811,28 @@
         <v>0</v>
       </c>
       <c r="H8" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I8" s="3">
         <v>4</v>
       </c>
       <c r="J8" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K8" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L8" s="3">
         <v>4</v>
       </c>
       <c r="M8" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
       <c r="O8" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P8" s="3">
         <v>4</v>
@@ -2844,28 +2844,28 @@
         <v>4</v>
       </c>
       <c r="S8" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
       <c r="V8" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W8" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X8" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y8" s="3">
         <v>4</v>
       </c>
       <c r="Z8" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="3">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>5</v>
       </c>
       <c r="F9" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I9" s="3">
         <v>5</v>
@@ -2927,7 +2927,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P9" s="3">
         <v>5</v>
@@ -2948,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W9" s="3">
         <v>5</v>
@@ -2960,7 +2960,7 @@
         <v>5</v>
       </c>
       <c r="Z9" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="3">
         <v>0</v>
@@ -2969,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="AC9" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD9" s="3">
         <v>5</v>
@@ -3046,16 +3046,16 @@
         <v>8</v>
       </c>
       <c r="W10" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X10" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z10" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="3">
         <v>0</v>
@@ -3067,10 +3067,10 @@
         <v>8</v>
       </c>
       <c r="AD10" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE10" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/target.xlsx
+++ b/target.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\백업폴더\딱따구리\AI\강북도매 영업관리 포털\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33180A0-2C35-48DF-97CC-DBDDC0D5EFC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33FEEAD-2496-470E-AA83-1743D4E54A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F51F585E-D8DA-4EE1-A615-D4BBA305B88C}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F51F585E-D8DA-4EE1-A615-D4BBA305B88C}"/>
   </bookViews>
   <sheets>
     <sheet name="무선목표" sheetId="2" r:id="rId1"/>
@@ -683,7 +683,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -704,6 +704,9 @@
     </xf>
     <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="150">
@@ -1146,276 +1149,283 @@
   <sheetPr>
     <tabColor theme="1"/>
   </sheetPr>
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:AF10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.58203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="31" width="5.25" style="1" customWidth="1"/>
-    <col min="32" max="16384" width="9" style="1"/>
+    <col min="32" max="32" width="5.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="5">
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="C1" s="5">
-        <v>46267</v>
+        <v>46297</v>
       </c>
       <c r="D1" s="5">
-        <v>46268</v>
+        <v>46298</v>
       </c>
       <c r="E1" s="5">
-        <v>46269</v>
+        <v>46299</v>
       </c>
       <c r="F1" s="5">
-        <v>46270</v>
+        <v>46300</v>
       </c>
       <c r="G1" s="5">
-        <v>46271</v>
+        <v>46301</v>
       </c>
       <c r="H1" s="5">
-        <v>46272</v>
+        <v>46302</v>
       </c>
       <c r="I1" s="5">
-        <v>46273</v>
+        <v>46303</v>
       </c>
       <c r="J1" s="5">
-        <v>46274</v>
+        <v>46304</v>
       </c>
       <c r="K1" s="5">
-        <v>46275</v>
+        <v>46305</v>
       </c>
       <c r="L1" s="5">
-        <v>46276</v>
+        <v>46306</v>
       </c>
       <c r="M1" s="5">
-        <v>46277</v>
+        <v>46307</v>
       </c>
       <c r="N1" s="5">
-        <v>46278</v>
+        <v>46308</v>
       </c>
       <c r="O1" s="5">
-        <v>46279</v>
+        <v>46309</v>
       </c>
       <c r="P1" s="5">
-        <v>46280</v>
+        <v>46310</v>
       </c>
       <c r="Q1" s="5">
-        <v>46281</v>
+        <v>46311</v>
       </c>
       <c r="R1" s="5">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="S1" s="5">
-        <v>46283</v>
+        <v>46313</v>
       </c>
       <c r="T1" s="5">
-        <v>46284</v>
+        <v>46314</v>
       </c>
       <c r="U1" s="5">
-        <v>46285</v>
+        <v>46315</v>
       </c>
       <c r="V1" s="5">
-        <v>46286</v>
+        <v>46316</v>
       </c>
       <c r="W1" s="5">
-        <v>46287</v>
+        <v>46317</v>
       </c>
       <c r="X1" s="5">
-        <v>46288</v>
+        <v>46318</v>
       </c>
       <c r="Y1" s="5">
-        <v>46289</v>
+        <v>46319</v>
       </c>
       <c r="Z1" s="5">
-        <v>46290</v>
+        <v>46320</v>
       </c>
       <c r="AA1" s="5">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="AB1" s="5">
-        <v>46292</v>
+        <v>46322</v>
       </c>
       <c r="AC1" s="5">
-        <v>46293</v>
+        <v>46323</v>
       </c>
       <c r="AD1" s="5">
-        <v>46294</v>
+        <v>46324</v>
       </c>
       <c r="AE1" s="5">
-        <v>46295</v>
+        <v>46325</v>
+      </c>
+      <c r="AF1" s="5">
+        <v>46326</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="6">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C2" s="6">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D2" s="6">
         <v>21</v>
       </c>
       <c r="E2" s="6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F2" s="6">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G2" s="6">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H2" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="I2" s="6">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J2" s="6">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K2" s="6">
         <v>21</v>
       </c>
       <c r="L2" s="6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M2" s="6">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="N2" s="6">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O2" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="P2" s="6">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="Q2" s="6">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="R2" s="6">
         <v>21</v>
       </c>
       <c r="S2" s="6">
+        <v>0</v>
+      </c>
+      <c r="T2" s="6">
+        <v>24</v>
+      </c>
+      <c r="U2" s="6">
+        <v>16</v>
+      </c>
+      <c r="V2" s="6">
+        <v>16</v>
+      </c>
+      <c r="W2" s="6">
+        <v>17</v>
+      </c>
+      <c r="X2" s="6">
+        <v>17</v>
+      </c>
+      <c r="Y2" s="6">
+        <v>22</v>
+      </c>
+      <c r="Z2" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="6">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="6">
+        <v>16</v>
+      </c>
+      <c r="AC2" s="6">
+        <v>16</v>
+      </c>
+      <c r="AD2" s="6">
+        <v>16</v>
+      </c>
+      <c r="AE2" s="6">
+        <v>16</v>
+      </c>
+      <c r="AF2" s="7">
         <v>21</v>
       </c>
-      <c r="T2" s="6">
-        <v>27</v>
-      </c>
-      <c r="U2" s="6">
-        <v>0</v>
-      </c>
-      <c r="V2" s="6">
-        <v>31</v>
-      </c>
-      <c r="W2" s="6">
-        <v>21</v>
-      </c>
-      <c r="X2" s="6">
-        <v>21</v>
-      </c>
-      <c r="Y2" s="6">
-        <v>20</v>
-      </c>
-      <c r="Z2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="6">
-        <v>32</v>
-      </c>
-      <c r="AD2" s="6">
-        <v>21</v>
-      </c>
-      <c r="AE2" s="6">
-        <v>21</v>
-      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C3" s="6">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D3" s="6">
         <v>19</v>
       </c>
       <c r="E3" s="6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F3" s="6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G3" s="6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H3" s="6">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I3" s="6">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J3" s="6">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K3" s="6">
         <v>19</v>
       </c>
       <c r="L3" s="6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M3" s="6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N3" s="6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O3" s="6">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="P3" s="6">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Q3" s="6">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="R3" s="6">
         <v>19</v>
       </c>
       <c r="S3" s="6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="T3" s="6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="U3" s="6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="V3" s="6">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="W3" s="6">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="X3" s="6">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Y3" s="6">
         <v>19</v>
@@ -1424,93 +1434,96 @@
         <v>0</v>
       </c>
       <c r="AA3" s="6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AB3" s="6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AC3" s="6">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="AD3" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE3" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF3" s="7">
         <v>19</v>
       </c>
-      <c r="AE3" s="6">
-        <v>19</v>
-      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C4" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D4" s="6">
         <v>15</v>
       </c>
       <c r="E4" s="6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F4" s="6">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G4" s="6">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H4" s="6">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I4" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J4" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K4" s="6">
         <v>15</v>
       </c>
       <c r="L4" s="6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M4" s="6">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N4" s="6">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O4" s="6">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="P4" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q4" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="R4" s="6">
         <v>15</v>
       </c>
       <c r="S4" s="6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="T4" s="6">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="U4" s="6">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V4" s="6">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="W4" s="6">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="X4" s="6">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y4" s="6">
         <v>15</v>
@@ -1519,93 +1532,96 @@
         <v>0</v>
       </c>
       <c r="AA4" s="6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AB4" s="6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC4" s="6">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AD4" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE4" s="6">
+        <v>11</v>
+      </c>
+      <c r="AF4" s="7">
         <v>15</v>
       </c>
-      <c r="AE4" s="6">
-        <v>15</v>
-      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C5" s="6">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D5" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F5" s="6">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G5" s="6">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H5" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I5" s="6">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J5" s="6">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K5" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L5" s="6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M5" s="6">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="N5" s="6">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O5" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="P5" s="6">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="Q5" s="6">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="R5" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S5" s="6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="T5" s="6">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="U5" s="6">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="V5" s="6">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="W5" s="6">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="X5" s="6">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Y5" s="6">
         <v>21</v>
@@ -1614,188 +1630,194 @@
         <v>0</v>
       </c>
       <c r="AA5" s="6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB5" s="6">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC5" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="AD5" s="6">
+        <v>16</v>
+      </c>
+      <c r="AE5" s="6">
+        <v>16</v>
+      </c>
+      <c r="AF5" s="7">
         <v>21</v>
       </c>
-      <c r="AE5" s="6">
-        <v>21</v>
-      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="6">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C6" s="6">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D6" s="6">
         <v>18</v>
       </c>
       <c r="E6" s="6">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F6" s="6">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G6" s="6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H6" s="6">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="I6" s="6">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J6" s="6">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K6" s="6">
         <v>18</v>
       </c>
       <c r="L6" s="6">
+        <v>0</v>
+      </c>
+      <c r="M6" s="6">
+        <v>20</v>
+      </c>
+      <c r="N6" s="6">
+        <v>14</v>
+      </c>
+      <c r="O6" s="6">
+        <v>14</v>
+      </c>
+      <c r="P6" s="6">
+        <v>14</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>14</v>
+      </c>
+      <c r="R6" s="6">
         <v>18</v>
       </c>
-      <c r="M6" s="6">
-        <v>23</v>
-      </c>
-      <c r="N6" s="6">
-        <v>0</v>
-      </c>
-      <c r="O6" s="6">
-        <v>27</v>
-      </c>
-      <c r="P6" s="6">
+      <c r="S6" s="6">
+        <v>0</v>
+      </c>
+      <c r="T6" s="6">
+        <v>20</v>
+      </c>
+      <c r="U6" s="6">
+        <v>14</v>
+      </c>
+      <c r="V6" s="6">
+        <v>14</v>
+      </c>
+      <c r="W6" s="6">
+        <v>14</v>
+      </c>
+      <c r="X6" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y6" s="6">
         <v>18</v>
       </c>
-      <c r="Q6" s="6">
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="6">
+        <v>20</v>
+      </c>
+      <c r="AB6" s="6">
+        <v>13</v>
+      </c>
+      <c r="AC6" s="6">
+        <v>13</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>13</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF6" s="7">
         <v>17</v>
       </c>
-      <c r="R6" s="6">
-        <v>17</v>
-      </c>
-      <c r="S6" s="6">
-        <v>17</v>
-      </c>
-      <c r="T6" s="6">
-        <v>23</v>
-      </c>
-      <c r="U6" s="6">
-        <v>0</v>
-      </c>
-      <c r="V6" s="6">
-        <v>27</v>
-      </c>
-      <c r="W6" s="6">
-        <v>17</v>
-      </c>
-      <c r="X6" s="6">
-        <v>17</v>
-      </c>
-      <c r="Y6" s="6">
-        <v>17</v>
-      </c>
-      <c r="Z6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="6">
-        <v>27</v>
-      </c>
-      <c r="AD6" s="6">
-        <v>18</v>
-      </c>
-      <c r="AE6" s="6">
-        <v>18</v>
-      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="6">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C7" s="6">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D7" s="6">
         <v>26</v>
       </c>
       <c r="E7" s="6">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F7" s="6">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G7" s="6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H7" s="6">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="I7" s="6">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J7" s="6">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K7" s="6">
         <v>26</v>
       </c>
       <c r="L7" s="6">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M7" s="6">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="N7" s="6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O7" s="6">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="P7" s="6">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="Q7" s="6">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="R7" s="6">
         <v>26</v>
       </c>
       <c r="S7" s="6">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T7" s="6">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="U7" s="6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V7" s="6">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="W7" s="6">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="X7" s="6">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="Y7" s="6">
         <v>26</v>
@@ -1804,283 +1826,292 @@
         <v>0</v>
       </c>
       <c r="AA7" s="6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AB7" s="6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC7" s="6">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="AD7" s="6">
+        <v>20</v>
+      </c>
+      <c r="AE7" s="6">
+        <v>20</v>
+      </c>
+      <c r="AF7" s="7">
         <v>26</v>
       </c>
-      <c r="AE7" s="6">
-        <v>26</v>
-      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="6">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C8" s="6">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D8" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" s="6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F8" s="6">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G8" s="6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H8" s="6">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="I8" s="6">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J8" s="6">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K8" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L8" s="6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M8" s="6">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N8" s="6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O8" s="6">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="P8" s="6">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q8" s="6">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="R8" s="6">
         <v>18</v>
       </c>
       <c r="S8" s="6">
+        <v>0</v>
+      </c>
+      <c r="T8" s="6">
+        <v>20</v>
+      </c>
+      <c r="U8" s="6">
+        <v>14</v>
+      </c>
+      <c r="V8" s="6">
+        <v>14</v>
+      </c>
+      <c r="W8" s="6">
+        <v>14</v>
+      </c>
+      <c r="X8" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y8" s="6">
         <v>18</v>
       </c>
-      <c r="T8" s="6">
-        <v>23</v>
-      </c>
-      <c r="U8" s="6">
-        <v>0</v>
-      </c>
-      <c r="V8" s="6">
-        <v>26</v>
-      </c>
-      <c r="W8" s="6">
+      <c r="Z8" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="6">
+        <v>20</v>
+      </c>
+      <c r="AB8" s="6">
+        <v>13</v>
+      </c>
+      <c r="AC8" s="6">
+        <v>13</v>
+      </c>
+      <c r="AD8" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE8" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF8" s="7">
         <v>17</v>
       </c>
-      <c r="X8" s="6">
-        <v>17</v>
-      </c>
-      <c r="Y8" s="6">
-        <v>17</v>
-      </c>
-      <c r="Z8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="6">
-        <v>27</v>
-      </c>
-      <c r="AD8" s="6">
-        <v>18</v>
-      </c>
-      <c r="AE8" s="6">
-        <v>18</v>
-      </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C9" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D9" s="6">
         <v>15</v>
       </c>
       <c r="E9" s="6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F9" s="6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G9" s="6">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H9" s="6">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I9" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J9" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K9" s="6">
         <v>15</v>
       </c>
       <c r="L9" s="6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M9" s="6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N9" s="6">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O9" s="6">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="P9" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q9" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="R9" s="6">
         <v>15</v>
       </c>
       <c r="S9" s="6">
+        <v>0</v>
+      </c>
+      <c r="T9" s="6">
+        <v>18</v>
+      </c>
+      <c r="U9" s="6">
+        <v>12</v>
+      </c>
+      <c r="V9" s="6">
+        <v>12</v>
+      </c>
+      <c r="W9" s="6">
+        <v>12</v>
+      </c>
+      <c r="X9" s="6">
+        <v>12</v>
+      </c>
+      <c r="Y9" s="6">
         <v>15</v>
       </c>
-      <c r="T9" s="6">
-        <v>20</v>
-      </c>
-      <c r="U9" s="6">
-        <v>0</v>
-      </c>
-      <c r="V9" s="6">
-        <v>24</v>
-      </c>
-      <c r="W9" s="6">
+      <c r="Z9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="6">
+        <v>18</v>
+      </c>
+      <c r="AB9" s="6">
+        <v>12</v>
+      </c>
+      <c r="AC9" s="6">
+        <v>12</v>
+      </c>
+      <c r="AD9" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE9" s="6">
+        <v>11</v>
+      </c>
+      <c r="AF9" s="7">
         <v>15</v>
       </c>
-      <c r="X9" s="6">
-        <v>15</v>
-      </c>
-      <c r="Y9" s="6">
-        <v>16</v>
-      </c>
-      <c r="Z9" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="6">
-        <v>24</v>
-      </c>
-      <c r="AD9" s="6">
-        <v>17</v>
-      </c>
-      <c r="AE9" s="6">
-        <v>16</v>
-      </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="6">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C10" s="6">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D10" s="6">
         <v>16</v>
       </c>
       <c r="E10" s="6">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F10" s="6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G10" s="6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H10" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="I10" s="6">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J10" s="6">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K10" s="6">
         <v>16</v>
       </c>
       <c r="L10" s="6">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M10" s="6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N10" s="6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O10" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="P10" s="6">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q10" s="6">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="R10" s="6">
         <v>16</v>
       </c>
       <c r="S10" s="6">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="T10" s="6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="U10" s="6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V10" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="W10" s="6">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="X10" s="6">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y10" s="6">
         <v>16</v>
@@ -2089,19 +2120,22 @@
         <v>0</v>
       </c>
       <c r="AA10" s="6">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AB10" s="6">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC10" s="6">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AD10" s="6">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AE10" s="6">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="AF10" s="7">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -2116,180 +2150,184 @@
   <sheetPr>
     <tabColor theme="1"/>
   </sheetPr>
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:AF10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="31" width="5.75" style="1" customWidth="1"/>
-    <col min="32" max="16384" width="9" style="1"/>
+    <col min="32" max="32" width="5.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="5">
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="C1" s="5">
-        <v>46267</v>
+        <v>46297</v>
       </c>
       <c r="D1" s="5">
-        <v>46268</v>
+        <v>46298</v>
       </c>
       <c r="E1" s="5">
-        <v>46269</v>
+        <v>46299</v>
       </c>
       <c r="F1" s="5">
-        <v>46270</v>
+        <v>46300</v>
       </c>
       <c r="G1" s="5">
-        <v>46271</v>
+        <v>46301</v>
       </c>
       <c r="H1" s="5">
-        <v>46272</v>
+        <v>46302</v>
       </c>
       <c r="I1" s="5">
-        <v>46273</v>
+        <v>46303</v>
       </c>
       <c r="J1" s="5">
-        <v>46274</v>
+        <v>46304</v>
       </c>
       <c r="K1" s="5">
-        <v>46275</v>
+        <v>46305</v>
       </c>
       <c r="L1" s="5">
-        <v>46276</v>
+        <v>46306</v>
       </c>
       <c r="M1" s="5">
-        <v>46277</v>
+        <v>46307</v>
       </c>
       <c r="N1" s="5">
-        <v>46278</v>
+        <v>46308</v>
       </c>
       <c r="O1" s="5">
-        <v>46279</v>
+        <v>46309</v>
       </c>
       <c r="P1" s="5">
-        <v>46280</v>
+        <v>46310</v>
       </c>
       <c r="Q1" s="5">
-        <v>46281</v>
+        <v>46311</v>
       </c>
       <c r="R1" s="5">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="S1" s="5">
-        <v>46283</v>
+        <v>46313</v>
       </c>
       <c r="T1" s="5">
-        <v>46284</v>
+        <v>46314</v>
       </c>
       <c r="U1" s="5">
-        <v>46285</v>
+        <v>46315</v>
       </c>
       <c r="V1" s="5">
-        <v>46286</v>
+        <v>46316</v>
       </c>
       <c r="W1" s="5">
-        <v>46287</v>
+        <v>46317</v>
       </c>
       <c r="X1" s="5">
-        <v>46288</v>
+        <v>46318</v>
       </c>
       <c r="Y1" s="5">
-        <v>46289</v>
+        <v>46319</v>
       </c>
       <c r="Z1" s="5">
-        <v>46290</v>
+        <v>46320</v>
       </c>
       <c r="AA1" s="5">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="AB1" s="5">
-        <v>46292</v>
+        <v>46322</v>
       </c>
       <c r="AC1" s="5">
-        <v>46293</v>
+        <v>46323</v>
       </c>
       <c r="AD1" s="5">
-        <v>46294</v>
+        <v>46324</v>
       </c>
       <c r="AE1" s="5">
-        <v>46295</v>
+        <v>46325</v>
+      </c>
+      <c r="AF1" s="5">
+        <v>46326</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3">
         <v>6</v>
       </c>
       <c r="E2" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3">
         <v>7</v>
       </c>
       <c r="G2" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H2" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I2" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J2" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M2" s="3">
         <v>7</v>
       </c>
       <c r="N2" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O2" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P2" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q2" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R2" s="3">
         <v>6</v>
       </c>
       <c r="S2" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T2" s="3">
         <v>7</v>
       </c>
       <c r="U2" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V2" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W2" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X2" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y2" s="3">
         <v>6</v>
@@ -2298,93 +2336,96 @@
         <v>0</v>
       </c>
       <c r="AA2" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB2" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC2" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AD2" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE2" s="3">
+        <v>4</v>
+      </c>
+      <c r="AF2" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3">
         <v>6</v>
       </c>
       <c r="E3" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H3" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I3" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J3" s="3">
+        <v>5</v>
+      </c>
+      <c r="K3" s="3">
+        <v>6</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
         <v>7</v>
       </c>
-      <c r="K3" s="3">
-        <v>6</v>
-      </c>
-      <c r="L3" s="3">
-        <v>6</v>
-      </c>
-      <c r="M3" s="3">
-        <v>8</v>
-      </c>
       <c r="N3" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O3" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="P3" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q3" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R3" s="3">
         <v>6</v>
       </c>
       <c r="S3" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T3" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U3" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V3" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W3" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X3" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y3" s="3">
         <v>6</v>
@@ -2393,93 +2434,96 @@
         <v>0</v>
       </c>
       <c r="AA3" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB3" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC3" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AD3" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE3" s="3">
+        <v>4</v>
+      </c>
+      <c r="AF3" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3">
         <v>5</v>
       </c>
       <c r="E4" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G4" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I4" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J4" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K4" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L4" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N4" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O4" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P4" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q4" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R4" s="3">
         <v>5</v>
       </c>
       <c r="S4" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V4" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W4" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X4" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y4" s="3">
         <v>5</v>
@@ -2488,93 +2532,96 @@
         <v>0</v>
       </c>
       <c r="AA4" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB4" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC4" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AD4" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE4" s="3">
+        <v>4</v>
+      </c>
+      <c r="AF4" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>6</v>
       </c>
       <c r="E5" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H5" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I5" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J5" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K5" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L5" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M5" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N5" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O5" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P5" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q5" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R5" s="3">
         <v>6</v>
       </c>
       <c r="S5" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T5" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U5" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V5" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W5" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X5" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5" s="3">
         <v>6</v>
@@ -2583,93 +2630,96 @@
         <v>0</v>
       </c>
       <c r="AA5" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB5" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC5" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AD5" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE5" s="3">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="AF5" s="3">
+        <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C6" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D6" s="3">
         <v>6</v>
       </c>
       <c r="E6" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3">
         <v>7</v>
       </c>
       <c r="G6" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H6" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I6" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J6" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M6" s="3">
         <v>7</v>
       </c>
       <c r="N6" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O6" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P6" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q6" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R6" s="3">
         <v>6</v>
       </c>
       <c r="S6" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T6" s="3">
         <v>7</v>
       </c>
       <c r="U6" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V6" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W6" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X6" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y6" s="3">
         <v>6</v>
@@ -2678,93 +2728,96 @@
         <v>0</v>
       </c>
       <c r="AA6" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB6" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC6" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AD6" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE6" s="3">
+        <v>4</v>
+      </c>
+      <c r="AF6" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="3">
         <v>7</v>
       </c>
       <c r="E7" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G7" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H7" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I7" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J7" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K7" s="3">
         <v>7</v>
       </c>
       <c r="L7" s="3">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3">
         <v>8</v>
       </c>
-      <c r="M7" s="3">
-        <v>10</v>
-      </c>
       <c r="N7" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O7" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P7" s="3">
+        <v>6</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>6</v>
+      </c>
+      <c r="R7" s="3">
+        <v>7</v>
+      </c>
+      <c r="S7" s="3">
+        <v>0</v>
+      </c>
+      <c r="T7" s="3">
         <v>8</v>
       </c>
-      <c r="Q7" s="3">
-        <v>8</v>
-      </c>
-      <c r="R7" s="3">
-        <v>8</v>
-      </c>
-      <c r="S7" s="3">
-        <v>8</v>
-      </c>
-      <c r="T7" s="3">
-        <v>10</v>
-      </c>
       <c r="U7" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V7" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="W7" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X7" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y7" s="3">
         <v>7</v>
@@ -2773,93 +2826,96 @@
         <v>0</v>
       </c>
       <c r="AA7" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AB7" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC7" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AD7" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE7" s="3">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="AF7" s="3">
+        <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="3">
         <v>4</v>
       </c>
       <c r="E8" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
         <v>5</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I8" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J8" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K8" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L8" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N8" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O8" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P8" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R8" s="3">
         <v>4</v>
       </c>
       <c r="S8" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T8" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U8" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V8" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W8" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X8" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y8" s="3">
         <v>4</v>
@@ -2868,93 +2924,96 @@
         <v>0</v>
       </c>
       <c r="AA8" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB8" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC8" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AD8" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE8" s="3">
         <v>4</v>
       </c>
+      <c r="AF8" s="3">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" s="3">
         <v>5</v>
       </c>
       <c r="E9" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G9" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I9" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J9" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K9" s="3">
         <v>5</v>
       </c>
       <c r="L9" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M9" s="3">
         <v>6</v>
       </c>
       <c r="N9" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O9" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P9" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q9" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R9" s="3">
         <v>5</v>
       </c>
       <c r="S9" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T9" s="3">
         <v>6</v>
       </c>
       <c r="U9" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V9" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W9" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X9" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y9" s="3">
         <v>5</v>
@@ -2963,114 +3022,120 @@
         <v>0</v>
       </c>
       <c r="AA9" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB9" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC9" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AD9" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE9" s="3">
+        <v>3</v>
+      </c>
+      <c r="AF9" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" s="3">
         <v>5</v>
       </c>
       <c r="E10" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G10" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I10" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K10" s="3">
         <v>5</v>
       </c>
       <c r="L10" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M10" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N10" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O10" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P10" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q10" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R10" s="3">
         <v>5</v>
       </c>
       <c r="S10" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T10" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U10" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V10" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W10" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X10" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y10" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z10" s="3">
         <v>0</v>
       </c>
       <c r="AA10" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB10" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC10" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AD10" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE10" s="3">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
